--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794706</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794720</v>
       </c>
       <c r="B3" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794706</v>
       </c>
       <c r="B2" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794720</v>
       </c>
       <c r="B3" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794706</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794720</v>
       </c>
       <c r="B3" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794706</v>
       </c>
       <c r="B2" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794720</v>
       </c>
       <c r="B3" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794706</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794720</v>
       </c>
       <c r="B3" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794706</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794720</v>
       </c>
       <c r="B3" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794706</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794720</v>
       </c>
       <c r="B3" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -939,11 +939,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1059,11 +1055,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1179,11 +1171,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794706</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794720</v>
       </c>
       <c r="B3" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794706</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794720</v>
       </c>
       <c r="B3" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33048-2026 artfynd.xlsx
+++ b/artfynd/A 33048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794706</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794720</v>
       </c>
       <c r="B3" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136794474</v>
       </c>
       <c r="B4" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136794600</v>
       </c>
       <c r="B5" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136794607</v>
       </c>
       <c r="B6" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
